--- a/files/Promoções_WhatsAppWeb.xlsx
+++ b/files/Promoções_WhatsAppWeb.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Lista de contatos WhatsApp</t>
   </si>
@@ -31,25 +31,34 @@
     <t>Sobrenome</t>
   </si>
   <si>
-    <t>Pai</t>
-  </si>
-  <si>
     <t>Mãe</t>
   </si>
   <si>
-    <t>81  98879-8884</t>
-  </si>
-  <si>
     <t>ZezeD</t>
   </si>
   <si>
-    <t>MárioD</t>
-  </si>
-  <si>
     <t>8198989898</t>
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>81 8664-1979</t>
+  </si>
+  <si>
+    <t>Vinicius</t>
+  </si>
+  <si>
+    <t>Consultor</t>
+  </si>
+  <si>
+    <t>81 9791-2535</t>
   </si>
 </sst>
 </file>
@@ -401,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -430,18 +439,18 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -449,10 +458,21 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
